--- a/GameConfig/Datas/运营/活动开启配置表.xlsx
+++ b/GameConfig/Datas/运营/活动开启配置表.xlsx
@@ -267,14 +267,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,7 +436,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -470,12 +463,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -639,12 +626,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -805,58 +786,61 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -865,73 +849,70 @@
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -940,11 +921,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -952,49 +933,49 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
